--- a/Assets/Excel sheets/Requests.xlsx
+++ b/Assets/Excel sheets/Requests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\RMIT\RMIT sem 2 2026\GDS6\VANDERBILT\Assets\Excel sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54272199-7A0E-463A-AEB1-6D68405F1577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950D707B-0B58-44E8-8EEC-CC02628EC6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7215" yWindow="2715" windowWidth="29190" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,20 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
-  <si>
-    <t>Faction requesting</t>
-  </si>
-  <si>
-    <t>Requested Resources</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Reward</t>
   </si>
   <si>
-    <t>Time Limit</t>
-  </si>
-  <si>
     <t>Dialogue</t>
   </si>
   <si>
@@ -91,22 +82,35 @@
   </si>
   <si>
     <t>Title</t>
+  </si>
+  <si>
+    <t>Faction</t>
+  </si>
+  <si>
+    <t>RequestedResources</t>
+  </si>
+  <si>
+    <t>RewardAmount</t>
+  </si>
+  <si>
+    <t>ConsequencesAmount</t>
+  </si>
+  <si>
+    <t>Repeatable</t>
+  </si>
+  <si>
+    <t>test5</t>
+  </si>
+  <si>
+    <t>TimeLimit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -167,17 +171,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -461,154 +462,217 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="51" customWidth="1"/>
-    <col min="7" max="9" width="23.5703125" customWidth="1"/>
-    <col min="10" max="10" width="51" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="23.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="3" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
       <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
         <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -654,7 +718,7 @@
     <row r="59" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/Excel sheets/Requests.xlsx
+++ b/Assets/Excel sheets/Requests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\RMIT\RMIT sem 2 2026\GDS6\VANDERBILT\Assets\Excel sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950D707B-0B58-44E8-8EEC-CC02628EC6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A0337B-E143-4F18-AE9D-A8E4B8E81CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7215" yWindow="2715" windowWidth="29190" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7215" yWindow="2715" windowWidth="30570" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,13 +465,15 @@
   <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="1" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="23.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
     <col min="12" max="12" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
